--- a/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
+++ b/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
@@ -773,14 +773,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45163.60884208804</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -821,23 +817,6 @@
     <row r="11" ht="23.25" customHeight="1" s="1">
       <c r="E11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -869,7 +848,7 @@
       </c>
       <c r="C30" s="27" t="n"/>
       <c r="D30" s="28" t="n">
-        <v>53</v>
+        <v>60.95</v>
       </c>
       <c r="E30" s="29" t="n"/>
       <c r="F30" s="29" t="n"/>
@@ -887,7 +866,7 @@
       </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="28" t="n">
-        <v>56.761</v>
+        <v>65.27500000000001</v>
       </c>
       <c r="E31" s="29" t="n"/>
       <c r="F31" s="29" t="n"/>
@@ -905,7 +884,7 @@
       </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="28" t="n">
-        <v>62.208</v>
+        <v>71.539</v>
       </c>
       <c r="E32" s="29" t="n"/>
       <c r="F32" s="29" t="n"/>
@@ -923,7 +902,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>91.858</v>
+        <v>105.637</v>
       </c>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -941,7 +920,7 @@
       </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="28" t="n">
-        <v>118.854</v>
+        <v>136.682</v>
       </c>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -959,7 +938,7 @@
       </c>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="28" t="n">
-        <v>167.597</v>
+        <v>192.737</v>
       </c>
       <c r="E35" s="29" t="n"/>
       <c r="F35" s="29" t="n"/>
@@ -977,7 +956,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="28" t="n">
-        <v>243.186</v>
+        <v>279.664</v>
       </c>
       <c r="E36" s="29" t="n"/>
       <c r="F36" s="29" t="n"/>
@@ -995,7 +974,7 @@
       </c>
       <c r="C37" s="27" t="n"/>
       <c r="D37" s="28" t="n">
-        <v>372.857</v>
+        <v>428.786</v>
       </c>
       <c r="E37" s="29" t="n"/>
       <c r="F37" s="29" t="n"/>
@@ -1017,8 +996,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1026,15 +1003,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="5" t="n"/>
     </row>
@@ -1043,17 +1011,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
+++ b/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
@@ -773,7 +773,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45237</v>
+        <v>45252</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
+++ b/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
@@ -773,7 +773,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
@@ -1011,17 +1011,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
+++ b/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
@@ -773,7 +773,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
@@ -1011,17 +1011,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
+++ b/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
@@ -773,10 +773,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
+        <v>45261.57773076731</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -817,6 +821,23 @@
     <row r="11" ht="23.25" customHeight="1" s="1">
       <c r="E11" s="13" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -848,7 +869,7 @@
       </c>
       <c r="C30" s="27" t="n"/>
       <c r="D30" s="28" t="n">
-        <v>60.95</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="E30" s="29" t="n"/>
       <c r="F30" s="29" t="n"/>
@@ -866,7 +887,7 @@
       </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="28" t="n">
-        <v>65.27500000000001</v>
+        <v>99.91</v>
       </c>
       <c r="E31" s="29" t="n"/>
       <c r="F31" s="29" t="n"/>
@@ -884,7 +905,7 @@
       </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="28" t="n">
-        <v>71.539</v>
+        <v>109.5</v>
       </c>
       <c r="E32" s="29" t="n"/>
       <c r="F32" s="29" t="n"/>
@@ -902,7 +923,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>105.637</v>
+        <v>161.69</v>
       </c>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -920,7 +941,7 @@
       </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="28" t="n">
-        <v>136.682</v>
+        <v>209.21</v>
       </c>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -938,7 +959,7 @@
       </c>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="28" t="n">
-        <v>192.737</v>
+        <v>295.01</v>
       </c>
       <c r="E35" s="29" t="n"/>
       <c r="F35" s="29" t="n"/>
@@ -956,7 +977,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="28" t="n">
-        <v>279.664</v>
+        <v>428.06</v>
       </c>
       <c r="E36" s="29" t="n"/>
       <c r="F36" s="29" t="n"/>
@@ -974,7 +995,7 @@
       </c>
       <c r="C37" s="27" t="n"/>
       <c r="D37" s="28" t="n">
-        <v>428.786</v>
+        <v>656.3200000000001</v>
       </c>
       <c r="E37" s="29" t="n"/>
       <c r="F37" s="29" t="n"/>
@@ -996,6 +1017,8 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1003,6 +1026,15 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="5" t="n"/>
     </row>
@@ -1011,17 +1043,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
+++ b/LISTAS/ma/GANCHO CONTRAVIENTO.xlsx
@@ -773,14 +773,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45261.57773076731</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -821,23 +817,6 @@
     <row r="11" ht="23.25" customHeight="1" s="1">
       <c r="E11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -869,7 +848,7 @@
       </c>
       <c r="C30" s="27" t="n"/>
       <c r="D30" s="28" t="n">
-        <v>93.29000000000001</v>
+        <v>60.95</v>
       </c>
       <c r="E30" s="29" t="n"/>
       <c r="F30" s="29" t="n"/>
@@ -887,7 +866,7 @@
       </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="28" t="n">
-        <v>99.91</v>
+        <v>65.27500000000001</v>
       </c>
       <c r="E31" s="29" t="n"/>
       <c r="F31" s="29" t="n"/>
@@ -905,7 +884,7 @@
       </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="28" t="n">
-        <v>109.5</v>
+        <v>71.539</v>
       </c>
       <c r="E32" s="29" t="n"/>
       <c r="F32" s="29" t="n"/>
@@ -923,7 +902,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>161.69</v>
+        <v>105.637</v>
       </c>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -941,7 +920,7 @@
       </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="28" t="n">
-        <v>209.21</v>
+        <v>136.682</v>
       </c>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -959,7 +938,7 @@
       </c>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="28" t="n">
-        <v>295.01</v>
+        <v>192.737</v>
       </c>
       <c r="E35" s="29" t="n"/>
       <c r="F35" s="29" t="n"/>
@@ -977,7 +956,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="28" t="n">
-        <v>428.06</v>
+        <v>279.664</v>
       </c>
       <c r="E36" s="29" t="n"/>
       <c r="F36" s="29" t="n"/>
@@ -995,7 +974,7 @@
       </c>
       <c r="C37" s="27" t="n"/>
       <c r="D37" s="28" t="n">
-        <v>656.3200000000001</v>
+        <v>428.786</v>
       </c>
       <c r="E37" s="29" t="n"/>
       <c r="F37" s="29" t="n"/>
@@ -1017,8 +996,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1026,15 +1003,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="5" t="n"/>
     </row>
@@ -1043,16 +1011,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
